--- a/experimentos/plan_financiero/salida/detalle_v11.xlsx
+++ b/experimentos/plan_financiero/salida/detalle_v11.xlsx
@@ -566,10 +566,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
       <c r="E2" t="n">
-        <v>2250</v>
+        <v>1125</v>
       </c>
       <c r="F2" t="n">
         <v>2600</v>
@@ -578,7 +578,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>617.5</v>
+        <v>373.75</v>
       </c>
       <c r="I2" t="n">
         <v>245.83</v>
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>5662.5</v>
+        <v>2831.25</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -608,7 +608,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3872.18</v>
+        <v>3577.24</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>54856.99</v>
+        <v>37983.18</v>
       </c>
     </row>
     <row r="3">
@@ -649,10 +649,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
       <c r="E3" t="n">
-        <v>2250</v>
+        <v>1125</v>
       </c>
       <c r="F3" t="n">
         <v>2600</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>617.5</v>
+        <v>373.75</v>
       </c>
       <c r="I3" t="n">
         <v>245.83</v>
@@ -682,16 +682,16 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5662.5</v>
+        <v>2831.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2737.5</v>
+        <v>1368.75</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3872.18</v>
+        <v>3577.24</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -718,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>42476.48</v>
+        <v>30097.61</v>
       </c>
     </row>
     <row r="4">
@@ -732,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
       <c r="E4" t="n">
-        <v>2250</v>
+        <v>1125</v>
       </c>
       <c r="F4" t="n">
         <v>2600</v>
@@ -744,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>617.5</v>
+        <v>373.75</v>
       </c>
       <c r="I4" t="n">
         <v>245.83</v>
@@ -765,16 +765,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5662.5</v>
+        <v>2831.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2737.5</v>
+        <v>1368.75</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3872.18</v>
+        <v>3577.24</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>30095.98</v>
+        <v>22212.04</v>
       </c>
     </row>
     <row r="5">
@@ -815,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
       <c r="E5" t="n">
-        <v>2250</v>
+        <v>1125</v>
       </c>
       <c r="F5" t="n">
         <v>2600</v>
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>617.5</v>
+        <v>373.75</v>
       </c>
       <c r="I5" t="n">
         <v>245.83</v>
@@ -848,16 +848,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>5662.5</v>
+        <v>2831.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2737.5</v>
+        <v>1368.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>4050</v>
+        <v>2025</v>
       </c>
       <c r="R5" t="n">
-        <v>3872.18</v>
+        <v>3577.24</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -884,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>13665.47</v>
+        <v>12301.47</v>
       </c>
     </row>
     <row r="6">
@@ -895,13 +895,13 @@
         <v>20000</v>
       </c>
       <c r="C6" t="n">
-        <v>1625</v>
+        <v>1637.5</v>
       </c>
       <c r="D6" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
       <c r="E6" t="n">
-        <v>2250</v>
+        <v>1125</v>
       </c>
       <c r="F6" t="n">
         <v>2600</v>
@@ -910,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>617.5</v>
+        <v>373.75</v>
       </c>
       <c r="I6" t="n">
         <v>245.83</v>
@@ -922,25 +922,25 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M6" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N6" t="n">
         <v>12100</v>
       </c>
       <c r="O6" t="n">
-        <v>5662.5</v>
+        <v>2831.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2737.5</v>
+        <v>1368.75</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3872.18</v>
+        <v>3577.24</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>13384.96</v>
+        <v>16515.9</v>
       </c>
     </row>
     <row r="7">
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1625</v>
+        <v>1637.5</v>
       </c>
       <c r="D7" t="n">
         <v>7500</v>
@@ -999,7 +999,7 @@
         <v>245.83</v>
       </c>
       <c r="J7" t="n">
-        <v>298.33</v>
+        <v>283.33</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1011,13 +1011,13 @@
         <v>2100</v>
       </c>
       <c r="N7" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O7" t="n">
         <v>5662.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2737.5</v>
+        <v>1368.75</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>298.33</v>
+        <v>283.33</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1047,10 +1047,10 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="AA7" t="n">
-        <v>74509.45</v>
+        <v>76205.64</v>
       </c>
     </row>
     <row r="8">
@@ -1061,7 +1061,7 @@
         <v>20000</v>
       </c>
       <c r="C8" t="n">
-        <v>3250</v>
+        <v>3275</v>
       </c>
       <c r="D8" t="n">
         <v>7500</v>
@@ -1082,16 +1082,16 @@
         <v>245.83</v>
       </c>
       <c r="J8" t="n">
-        <v>298.33</v>
+        <v>283.33</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M8" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N8" t="n">
         <v>12100</v>
@@ -1103,13 +1103,13 @@
         <v>2737.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>4050</v>
+        <v>2700</v>
       </c>
       <c r="R8" t="n">
         <v>3872.18</v>
       </c>
       <c r="S8" t="n">
-        <v>6466.95</v>
+        <v>6754.39</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>63711.99</v>
+        <v>66470.74000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>3250</v>
+        <v>3275</v>
       </c>
       <c r="D9" t="n">
         <v>7500</v>
@@ -1165,7 +1165,7 @@
         <v>245.83</v>
       </c>
       <c r="J9" t="n">
-        <v>298.33</v>
+        <v>283.33</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
         <v>2100</v>
       </c>
       <c r="N9" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O9" t="n">
         <v>5662.5</v>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>87026.48</v>
+        <v>89966.73</v>
       </c>
     </row>
     <row r="10">
@@ -1227,7 +1227,7 @@
         <v>20000</v>
       </c>
       <c r="C10" t="n">
-        <v>4875</v>
+        <v>4912.5</v>
       </c>
       <c r="D10" t="n">
         <v>7500</v>
@@ -1248,16 +1248,16 @@
         <v>245.83</v>
       </c>
       <c r="J10" t="n">
-        <v>298.33</v>
+        <v>283.33</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M10" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N10" t="n">
         <v>12100</v>
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>678.33</v>
+        <v>633.33</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1299,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>86175.98</v>
+        <v>89161.23</v>
       </c>
     </row>
     <row r="11">
@@ -1310,7 +1310,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4875</v>
+        <v>4912.5</v>
       </c>
       <c r="D11" t="n">
         <v>7500</v>
@@ -1331,7 +1331,7 @@
         <v>245.83</v>
       </c>
       <c r="J11" t="n">
-        <v>298.33</v>
+        <v>283.33</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O11" t="n">
         <v>5662.5</v>
@@ -1358,7 +1358,7 @@
         <v>3872.18</v>
       </c>
       <c r="S11" t="n">
-        <v>12525.98</v>
+        <v>12588.98</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>92914.49000000001</v>
+        <v>96018.24000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>4875</v>
+        <v>4912.5</v>
       </c>
       <c r="D12" t="n">
         <v>7500</v>
@@ -1414,7 +1414,7 @@
         <v>245.83</v>
       </c>
       <c r="J12" t="n">
-        <v>298.33</v>
+        <v>283.33</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>80533.98</v>
+        <v>83637.73</v>
       </c>
     </row>
     <row r="13">
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>4875</v>
+        <v>4912.5</v>
       </c>
       <c r="D13" t="n">
         <v>7500</v>
@@ -1497,7 +1497,7 @@
         <v>245.83</v>
       </c>
       <c r="J13" t="n">
-        <v>298.33</v>
+        <v>283.33</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>678.33</v>
+        <v>633.33</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>313953.47</v>
+        <v>317102.22</v>
       </c>
     </row>
     <row r="14">
@@ -1559,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>4875</v>
+        <v>4912.5</v>
       </c>
       <c r="D14" t="n">
         <v>10000</v>
@@ -1571,16 +1571,16 @@
         <v>4733.33</v>
       </c>
       <c r="G14" t="n">
-        <v>487.5</v>
+        <v>491.25</v>
       </c>
       <c r="H14" t="n">
-        <v>911.04</v>
+        <v>911.23</v>
       </c>
       <c r="I14" t="n">
         <v>291.67</v>
       </c>
       <c r="J14" t="n">
-        <v>298.33</v>
+        <v>283.33</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
         <v>4050</v>
       </c>
       <c r="R14" t="n">
-        <v>7384.57</v>
+        <v>7389.33</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>288681.41</v>
+        <v>291825.39</v>
       </c>
     </row>
     <row r="15">
@@ -1642,7 +1642,7 @@
         <v>20000</v>
       </c>
       <c r="C15" t="n">
-        <v>6500</v>
+        <v>6550</v>
       </c>
       <c r="D15" t="n">
         <v>10000</v>
@@ -1654,25 +1654,25 @@
         <v>4733.33</v>
       </c>
       <c r="G15" t="n">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="H15" t="n">
-        <v>919.17</v>
+        <v>919.42</v>
       </c>
       <c r="I15" t="n">
         <v>300</v>
       </c>
       <c r="J15" t="n">
-        <v>296.08</v>
+        <v>281.08</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M15" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N15" t="n">
         <v>12100</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>7591.02</v>
+        <v>7597.38</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>280257.64</v>
+        <v>283395.27</v>
       </c>
     </row>
     <row r="16">
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>6500</v>
+        <v>6550</v>
       </c>
       <c r="D16" t="n">
         <v>10000</v>
@@ -1737,16 +1737,16 @@
         <v>4733.33</v>
       </c>
       <c r="G16" t="n">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="H16" t="n">
-        <v>919.17</v>
+        <v>919.42</v>
       </c>
       <c r="I16" t="n">
         <v>300</v>
       </c>
       <c r="J16" t="n">
-        <v>293.82</v>
+        <v>278.82</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
         <v>2100</v>
       </c>
       <c r="N16" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O16" t="n">
         <v>7550</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>7591.02</v>
+        <v>7597.38</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>673.8200000000001</v>
+        <v>628.8200000000001</v>
       </c>
       <c r="W16" t="n">
         <v>416.67</v>
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>296071.13</v>
+        <v>299428.91</v>
       </c>
     </row>
     <row r="17">
@@ -1808,7 +1808,7 @@
         <v>20000</v>
       </c>
       <c r="C17" t="n">
-        <v>8125</v>
+        <v>8187.5</v>
       </c>
       <c r="D17" t="n">
         <v>10000</v>
@@ -1820,25 +1820,25 @@
         <v>4733.33</v>
       </c>
       <c r="G17" t="n">
-        <v>812.5</v>
+        <v>818.75</v>
       </c>
       <c r="H17" t="n">
-        <v>927.29</v>
+        <v>927.6</v>
       </c>
       <c r="I17" t="n">
         <v>300</v>
       </c>
       <c r="J17" t="n">
-        <v>291.56</v>
+        <v>276.56</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M17" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N17" t="n">
         <v>12100</v>
@@ -1853,10 +1853,10 @@
         <v>5400</v>
       </c>
       <c r="R17" t="n">
-        <v>7797.48</v>
+        <v>7805.42</v>
       </c>
       <c r="S17" t="n">
-        <v>3236.23</v>
+        <v>3264.7</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1880,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>280019.19</v>
+        <v>283340.56</v>
       </c>
     </row>
     <row r="18">
@@ -1891,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>8125</v>
+        <v>8187.5</v>
       </c>
       <c r="D18" t="n">
         <v>10000</v>
@@ -1903,28 +1903,28 @@
         <v>4733.33</v>
       </c>
       <c r="G18" t="n">
-        <v>812.5</v>
+        <v>818.75</v>
       </c>
       <c r="H18" t="n">
-        <v>927.29</v>
+        <v>927.6</v>
       </c>
       <c r="I18" t="n">
         <v>300</v>
       </c>
       <c r="J18" t="n">
-        <v>289.31</v>
+        <v>274.31</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M18" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N18" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O18" t="n">
         <v>7550</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>7797.48</v>
+        <v>7805.42</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>296200.73</v>
+        <v>299695.66</v>
       </c>
     </row>
     <row r="19">
@@ -1974,7 +1974,7 @@
         <v>20000</v>
       </c>
       <c r="C19" t="n">
-        <v>9750</v>
+        <v>9825</v>
       </c>
       <c r="D19" t="n">
         <v>10000</v>
@@ -1986,28 +1986,28 @@
         <v>4733.33</v>
       </c>
       <c r="G19" t="n">
-        <v>975</v>
+        <v>982.5</v>
       </c>
       <c r="H19" t="n">
-        <v>935.42</v>
+        <v>935.79</v>
       </c>
       <c r="I19" t="n">
         <v>300</v>
       </c>
       <c r="J19" t="n">
-        <v>287.05</v>
+        <v>272.05</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M19" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N19" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O19" t="n">
         <v>7550</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>8003.94</v>
+        <v>8013.47</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>667.05</v>
+        <v>622.05</v>
       </c>
       <c r="W19" t="n">
         <v>416.67</v>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>311608.08</v>
+        <v>315319.98</v>
       </c>
     </row>
     <row r="20">
@@ -2057,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>9750</v>
+        <v>9825</v>
       </c>
       <c r="D20" t="n">
         <v>10000</v>
@@ -2069,28 +2069,28 @@
         <v>4733.33</v>
       </c>
       <c r="G20" t="n">
-        <v>975</v>
+        <v>982.5</v>
       </c>
       <c r="H20" t="n">
-        <v>935.42</v>
+        <v>935.79</v>
       </c>
       <c r="I20" t="n">
         <v>300</v>
       </c>
       <c r="J20" t="n">
-        <v>284.79</v>
+        <v>269.79</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M20" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N20" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O20" t="n">
         <v>7550</v>
@@ -2102,10 +2102,10 @@
         <v>5400</v>
       </c>
       <c r="R20" t="n">
-        <v>8003.94</v>
+        <v>8013.47</v>
       </c>
       <c r="S20" t="n">
-        <v>14576.1</v>
+        <v>14666.19</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>307611.58</v>
+        <v>311405.37</v>
       </c>
     </row>
     <row r="21">
@@ -2140,7 +2140,7 @@
         <v>20000</v>
       </c>
       <c r="C21" t="n">
-        <v>11375</v>
+        <v>11462.5</v>
       </c>
       <c r="D21" t="n">
         <v>10000</v>
@@ -2152,28 +2152,28 @@
         <v>4733.33</v>
       </c>
       <c r="G21" t="n">
-        <v>1137.5</v>
+        <v>1146.25</v>
       </c>
       <c r="H21" t="n">
-        <v>943.54</v>
+        <v>943.98</v>
       </c>
       <c r="I21" t="n">
         <v>300</v>
       </c>
       <c r="J21" t="n">
-        <v>282.53</v>
+        <v>267.53</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M21" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N21" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O21" t="n">
         <v>7550</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>8210.389999999999</v>
+        <v>8221.51</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>323386.99</v>
+        <v>327351.16</v>
       </c>
     </row>
     <row r="22">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>9750</v>
+        <v>9825</v>
       </c>
       <c r="D22" t="n">
         <v>10000</v>
@@ -2235,16 +2235,16 @@
         <v>4733.33</v>
       </c>
       <c r="G22" t="n">
-        <v>975</v>
+        <v>982.5</v>
       </c>
       <c r="H22" t="n">
-        <v>935.42</v>
+        <v>935.79</v>
       </c>
       <c r="I22" t="n">
         <v>300</v>
       </c>
       <c r="J22" t="n">
-        <v>280.28</v>
+        <v>265.28</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
         <v>2100</v>
       </c>
       <c r="N22" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O22" t="n">
         <v>7550</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>8003.94</v>
+        <v>8013.47</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>660.28</v>
+        <v>615.28</v>
       </c>
       <c r="W22" t="n">
         <v>416.67</v>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>338801.11</v>
+        <v>342982.24</v>
       </c>
     </row>
     <row r="23">
@@ -2306,7 +2306,7 @@
         <v>20000</v>
       </c>
       <c r="C23" t="n">
-        <v>11375</v>
+        <v>11462.5</v>
       </c>
       <c r="D23" t="n">
         <v>10000</v>
@@ -2318,25 +2318,25 @@
         <v>4733.33</v>
       </c>
       <c r="G23" t="n">
-        <v>1137.5</v>
+        <v>1146.25</v>
       </c>
       <c r="H23" t="n">
-        <v>943.54</v>
+        <v>943.98</v>
       </c>
       <c r="I23" t="n">
         <v>300</v>
       </c>
       <c r="J23" t="n">
-        <v>278.02</v>
+        <v>263.02</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M23" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N23" t="n">
         <v>12100</v>
@@ -2351,10 +2351,10 @@
         <v>5400</v>
       </c>
       <c r="R23" t="n">
-        <v>8210.389999999999</v>
+        <v>8221.51</v>
       </c>
       <c r="S23" t="n">
-        <v>10373.61</v>
+        <v>10431.37</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>315212.42</v>
+        <v>319324.68</v>
       </c>
     </row>
     <row r="24">
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>11375</v>
+        <v>11462.5</v>
       </c>
       <c r="D24" t="n">
         <v>10000</v>
@@ -2401,16 +2401,16 @@
         <v>4733.33</v>
       </c>
       <c r="G24" t="n">
-        <v>1137.5</v>
+        <v>1146.25</v>
       </c>
       <c r="H24" t="n">
-        <v>943.54</v>
+        <v>943.98</v>
       </c>
       <c r="I24" t="n">
         <v>300</v>
       </c>
       <c r="J24" t="n">
-        <v>275.76</v>
+        <v>260.76</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2422,7 +2422,7 @@
         <v>2100</v>
       </c>
       <c r="N24" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O24" t="n">
         <v>7550</v>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>8210.389999999999</v>
+        <v>8221.51</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>330994.59</v>
+        <v>335277.24</v>
       </c>
     </row>
     <row r="25">
@@ -2472,7 +2472,7 @@
         <v>20000</v>
       </c>
       <c r="C25" t="n">
-        <v>13000</v>
+        <v>13100</v>
       </c>
       <c r="D25" t="n">
         <v>10000</v>
@@ -2484,25 +2484,25 @@
         <v>4733.33</v>
       </c>
       <c r="G25" t="n">
-        <v>1300</v>
+        <v>1310</v>
       </c>
       <c r="H25" t="n">
-        <v>951.67</v>
+        <v>952.17</v>
       </c>
       <c r="I25" t="n">
         <v>300</v>
       </c>
       <c r="J25" t="n">
-        <v>273.51</v>
+        <v>258.51</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M25" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N25" t="n">
         <v>12100</v>
@@ -2517,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>8416.85</v>
+        <v>8429.559999999999</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>653.51</v>
+        <v>608.51</v>
       </c>
       <c r="W25" t="n">
         <v>416.67</v>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>322407.57</v>
+        <v>326722.51</v>
       </c>
     </row>
     <row r="26">
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>13000</v>
+        <v>13100</v>
       </c>
       <c r="D26" t="n">
         <v>13000</v>
@@ -2567,16 +2567,16 @@
         <v>6300</v>
       </c>
       <c r="G26" t="n">
-        <v>1300</v>
+        <v>1310</v>
       </c>
       <c r="H26" t="n">
-        <v>1225</v>
+        <v>1225.5</v>
       </c>
       <c r="I26" t="n">
         <v>345.83</v>
       </c>
       <c r="J26" t="n">
-        <v>271.25</v>
+        <v>256.25</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2588,7 +2588,7 @@
         <v>2100</v>
       </c>
       <c r="N26" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O26" t="n">
         <v>9815</v>
@@ -2600,10 +2600,10 @@
         <v>5400</v>
       </c>
       <c r="R26" t="n">
-        <v>10643.25</v>
+        <v>10655.95</v>
       </c>
       <c r="S26" t="n">
-        <v>10266.11</v>
+        <v>10323.05</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>314805.29</v>
+        <v>319232.09</v>
       </c>
     </row>
     <row r="27">
@@ -2638,7 +2638,7 @@
         <v>20000</v>
       </c>
       <c r="C27" t="n">
-        <v>13000</v>
+        <v>13100</v>
       </c>
       <c r="D27" t="n">
         <v>13000</v>
@@ -2650,25 +2650,25 @@
         <v>6300</v>
       </c>
       <c r="G27" t="n">
-        <v>1300</v>
+        <v>1310</v>
       </c>
       <c r="H27" t="n">
-        <v>1225</v>
+        <v>1225.5</v>
       </c>
       <c r="I27" t="n">
         <v>345.83</v>
       </c>
       <c r="J27" t="n">
-        <v>268.99</v>
+        <v>253.99</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>39500</v>
+        <v>39650</v>
       </c>
       <c r="M27" t="n">
-        <v>8295</v>
+        <v>8326.5</v>
       </c>
       <c r="N27" t="n">
         <v>12100</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>10643.25</v>
+        <v>10655.95</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>301206.38</v>
+        <v>305620.47</v>
       </c>
     </row>
     <row r="28">
@@ -2721,7 +2721,7 @@
         <v>20000</v>
       </c>
       <c r="C28" t="n">
-        <v>14625</v>
+        <v>14737.5</v>
       </c>
       <c r="D28" t="n">
         <v>13000</v>
@@ -2733,28 +2733,28 @@
         <v>6300</v>
       </c>
       <c r="G28" t="n">
-        <v>1462.5</v>
+        <v>1473.75</v>
       </c>
       <c r="H28" t="n">
-        <v>1233.12</v>
+        <v>1233.69</v>
       </c>
       <c r="I28" t="n">
         <v>345.83</v>
       </c>
       <c r="J28" t="n">
-        <v>266.74</v>
+        <v>251.74</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M28" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N28" t="n">
-        <v>47795</v>
+        <v>47976.5</v>
       </c>
       <c r="O28" t="n">
         <v>9815</v>
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>10849.71</v>
+        <v>10864</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>646.74</v>
+        <v>601.74</v>
       </c>
       <c r="W28" t="n">
         <v>416.67</v>
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>322528.27</v>
+        <v>327154.57</v>
       </c>
     </row>
     <row r="29">
@@ -2804,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>14625</v>
+        <v>14737.5</v>
       </c>
       <c r="D29" t="n">
         <v>13000</v>
@@ -2816,28 +2816,28 @@
         <v>6300</v>
       </c>
       <c r="G29" t="n">
-        <v>1462.5</v>
+        <v>1473.75</v>
       </c>
       <c r="H29" t="n">
-        <v>1233.12</v>
+        <v>1233.69</v>
       </c>
       <c r="I29" t="n">
         <v>345.83</v>
       </c>
       <c r="J29" t="n">
-        <v>264.48</v>
+        <v>249.48</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M29" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N29" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O29" t="n">
         <v>9815</v>
@@ -2849,10 +2849,10 @@
         <v>7020</v>
       </c>
       <c r="R29" t="n">
-        <v>10849.71</v>
+        <v>10864</v>
       </c>
       <c r="S29" t="n">
-        <v>10574.42</v>
+        <v>10630.53</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>314728</v>
+        <v>319465.4</v>
       </c>
     </row>
     <row r="30">
@@ -2887,7 +2887,7 @@
         <v>20000</v>
       </c>
       <c r="C30" t="n">
-        <v>16250</v>
+        <v>16375</v>
       </c>
       <c r="D30" t="n">
         <v>13000</v>
@@ -2899,28 +2899,28 @@
         <v>6300</v>
       </c>
       <c r="G30" t="n">
-        <v>1625</v>
+        <v>1637.5</v>
       </c>
       <c r="H30" t="n">
-        <v>1241.25</v>
+        <v>1241.88</v>
       </c>
       <c r="I30" t="n">
         <v>345.83</v>
       </c>
       <c r="J30" t="n">
-        <v>262.22</v>
+        <v>247.22</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>59000</v>
+        <v>59300</v>
       </c>
       <c r="M30" t="n">
-        <v>12390</v>
+        <v>12453</v>
       </c>
       <c r="N30" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O30" t="n">
         <v>9815</v>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>11056.16</v>
+        <v>11072.04</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2959,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>324317.95</v>
+        <v>329220.96</v>
       </c>
     </row>
     <row r="31">
@@ -2970,7 +2970,7 @@
         <v>20000</v>
       </c>
       <c r="C31" t="n">
-        <v>17875</v>
+        <v>18012.5</v>
       </c>
       <c r="D31" t="n">
         <v>13000</v>
@@ -2982,28 +2982,28 @@
         <v>6300</v>
       </c>
       <c r="G31" t="n">
-        <v>1787.5</v>
+        <v>1801.25</v>
       </c>
       <c r="H31" t="n">
-        <v>1249.38</v>
+        <v>1250.06</v>
       </c>
       <c r="I31" t="n">
         <v>345.83</v>
       </c>
       <c r="J31" t="n">
-        <v>259.97</v>
+        <v>244.97</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>49000</v>
+        <v>49300</v>
       </c>
       <c r="M31" t="n">
-        <v>10290</v>
+        <v>10353</v>
       </c>
       <c r="N31" t="n">
-        <v>71390</v>
+        <v>71753</v>
       </c>
       <c r="O31" t="n">
         <v>9815</v>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>11262.62</v>
+        <v>11280.09</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3027,7 +3027,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>639.97</v>
+        <v>594.97</v>
       </c>
       <c r="W31" t="n">
         <v>416.67</v>
@@ -3042,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>368828.7</v>
+        <v>374122.24</v>
       </c>
     </row>
     <row r="32">
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>17875</v>
+        <v>18012.5</v>
       </c>
       <c r="D32" t="n">
         <v>13000</v>
@@ -3065,28 +3065,28 @@
         <v>6300</v>
       </c>
       <c r="G32" t="n">
-        <v>1787.5</v>
+        <v>1801.25</v>
       </c>
       <c r="H32" t="n">
-        <v>1249.38</v>
+        <v>1250.06</v>
       </c>
       <c r="I32" t="n">
         <v>345.83</v>
       </c>
       <c r="J32" t="n">
-        <v>257.71</v>
+        <v>242.71</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M32" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N32" t="n">
-        <v>59290</v>
+        <v>59653</v>
       </c>
       <c r="O32" t="n">
         <v>9815</v>
@@ -3098,10 +3098,10 @@
         <v>7020</v>
       </c>
       <c r="R32" t="n">
-        <v>11262.62</v>
+        <v>11280.09</v>
       </c>
       <c r="S32" t="n">
-        <v>23205.26</v>
+        <v>23354.49</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -3125,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>371586.44</v>
+        <v>377076.29</v>
       </c>
     </row>
     <row r="33">
@@ -3136,7 +3136,7 @@
         <v>20000</v>
       </c>
       <c r="C33" t="n">
-        <v>19500</v>
+        <v>19650</v>
       </c>
       <c r="D33" t="n">
         <v>13000</v>
@@ -3148,28 +3148,28 @@
         <v>6300</v>
       </c>
       <c r="G33" t="n">
-        <v>1950</v>
+        <v>1965</v>
       </c>
       <c r="H33" t="n">
-        <v>1257.5</v>
+        <v>1258.25</v>
       </c>
       <c r="I33" t="n">
         <v>345.83</v>
       </c>
       <c r="J33" t="n">
-        <v>255.45</v>
+        <v>240.45</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>59000</v>
+        <v>59300</v>
       </c>
       <c r="M33" t="n">
-        <v>12390</v>
+        <v>12453</v>
       </c>
       <c r="N33" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O33" t="n">
         <v>9815</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>11469.08</v>
+        <v>11488.13</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -3208,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>380770.25</v>
+        <v>386422.54</v>
       </c>
     </row>
     <row r="34">
@@ -3219,7 +3219,7 @@
         <v>20000</v>
       </c>
       <c r="C34" t="n">
-        <v>21125</v>
+        <v>21287.5</v>
       </c>
       <c r="D34" t="n">
         <v>13000</v>
@@ -3231,28 +3231,28 @@
         <v>6300</v>
       </c>
       <c r="G34" t="n">
-        <v>2112.5</v>
+        <v>2128.75</v>
       </c>
       <c r="H34" t="n">
-        <v>1265.62</v>
+        <v>1266.44</v>
       </c>
       <c r="I34" t="n">
         <v>345.83</v>
       </c>
       <c r="J34" t="n">
-        <v>253.19</v>
+        <v>238.19</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M34" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N34" t="n">
-        <v>71390</v>
+        <v>71753</v>
       </c>
       <c r="O34" t="n">
         <v>9815</v>
@@ -3264,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>11675.53</v>
+        <v>11696.18</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3276,10 +3276,10 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>633.1900000000001</v>
+        <v>588.1900000000001</v>
       </c>
       <c r="W34" t="n">
-        <v>2316.67</v>
+        <v>2166.67</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>422974.86</v>
+        <v>429164.5</v>
       </c>
     </row>
     <row r="35">
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>21125</v>
+        <v>21287.5</v>
       </c>
       <c r="D35" t="n">
         <v>13000</v>
@@ -3314,28 +3314,28 @@
         <v>6300</v>
       </c>
       <c r="G35" t="n">
-        <v>2112.5</v>
+        <v>2128.75</v>
       </c>
       <c r="H35" t="n">
-        <v>1265.62</v>
+        <v>1266.44</v>
       </c>
       <c r="I35" t="n">
         <v>345.83</v>
       </c>
       <c r="J35" t="n">
-        <v>241.44</v>
+        <v>227.19</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>29500</v>
+        <v>29650</v>
       </c>
       <c r="M35" t="n">
-        <v>6195</v>
+        <v>6226.5</v>
       </c>
       <c r="N35" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O35" t="n">
         <v>9815</v>
@@ -3347,10 +3347,10 @@
         <v>7020</v>
       </c>
       <c r="R35" t="n">
-        <v>11675.53</v>
+        <v>11696.18</v>
       </c>
       <c r="S35" t="n">
-        <v>18895.27</v>
+        <v>19011.35</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>406041.45</v>
+        <v>412275.86</v>
       </c>
     </row>
     <row r="36">
@@ -3385,7 +3385,7 @@
         <v>20000</v>
       </c>
       <c r="C36" t="n">
-        <v>22750</v>
+        <v>22925</v>
       </c>
       <c r="D36" t="n">
         <v>13000</v>
@@ -3397,28 +3397,28 @@
         <v>6300</v>
       </c>
       <c r="G36" t="n">
-        <v>2275</v>
+        <v>2292.5</v>
       </c>
       <c r="H36" t="n">
-        <v>1273.75</v>
+        <v>1274.62</v>
       </c>
       <c r="I36" t="n">
         <v>345.83</v>
       </c>
       <c r="J36" t="n">
-        <v>239.18</v>
+        <v>224.93</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>39500</v>
+        <v>39650</v>
       </c>
       <c r="M36" t="n">
-        <v>8295</v>
+        <v>8326.5</v>
       </c>
       <c r="N36" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="O36" t="n">
         <v>9815</v>
@@ -3430,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>11881.99</v>
+        <v>11904.22</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>414819.11</v>
+        <v>421212.8</v>
       </c>
     </row>
     <row r="37">
@@ -3468,7 +3468,7 @@
         <v>20000</v>
       </c>
       <c r="C37" t="n">
-        <v>24375</v>
+        <v>24562.5</v>
       </c>
       <c r="D37" t="n">
         <v>13000</v>
@@ -3480,28 +3480,28 @@
         <v>6300</v>
       </c>
       <c r="G37" t="n">
-        <v>2437.5</v>
+        <v>2456.25</v>
       </c>
       <c r="H37" t="n">
-        <v>1281.88</v>
+        <v>1282.81</v>
       </c>
       <c r="I37" t="n">
         <v>345.83</v>
       </c>
       <c r="J37" t="n">
-        <v>236.92</v>
+        <v>222.67</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>49000</v>
+        <v>49300</v>
       </c>
       <c r="M37" t="n">
-        <v>10290</v>
+        <v>10353</v>
       </c>
       <c r="N37" t="n">
-        <v>47795</v>
+        <v>47976.5</v>
       </c>
       <c r="O37" t="n">
         <v>9815</v>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>12088.44</v>
+        <v>12112.27</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3525,10 +3525,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>597.92</v>
+        <v>555.17</v>
       </c>
       <c r="W37" t="n">
-        <v>2316.67</v>
+        <v>2166.67</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>433051.08</v>
+        <v>439795.19</v>
       </c>
     </row>
   </sheetData>
@@ -3699,16 +3699,16 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>64500</v>
+        <v>44500</v>
       </c>
       <c r="H2" t="n">
-        <v>78500</v>
+        <v>58500</v>
       </c>
       <c r="I2" t="n">
         <v>3000</v>
       </c>
       <c r="J2" t="n">
-        <v>57000</v>
+        <v>37000</v>
       </c>
       <c r="K2" t="n">
         <v>-1500</v>
@@ -3720,10 +3720,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>58500</v>
+        <v>38500</v>
       </c>
       <c r="O2" t="n">
-        <v>58500</v>
+        <v>38500</v>
       </c>
       <c r="P2" t="n">
         <v>1500</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>78500</v>
+        <v>58500</v>
       </c>
     </row>
     <row r="3">
@@ -3770,19 +3770,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>654.67</v>
+        <v>603.49</v>
       </c>
       <c r="G3" t="n">
-        <v>54856.99</v>
+        <v>37983.18</v>
       </c>
       <c r="H3" t="n">
-        <v>69265.83</v>
+        <v>52340.83</v>
       </c>
       <c r="I3" t="n">
         <v>3000</v>
       </c>
       <c r="J3" t="n">
-        <v>57000</v>
+        <v>37000</v>
       </c>
       <c r="K3" t="n">
         <v>-1500</v>
@@ -3791,13 +3791,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-13321.67</v>
+        <v>-8202.92</v>
       </c>
       <c r="N3" t="n">
-        <v>45178.33</v>
+        <v>30297.08</v>
       </c>
       <c r="O3" t="n">
-        <v>45178.33</v>
+        <v>30297.08</v>
       </c>
       <c r="P3" t="n">
         <v>1500</v>
@@ -3818,13 +3818,13 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1350</v>
+        <v>675</v>
       </c>
       <c r="W3" t="n">
-        <v>2737.5</v>
+        <v>1368.75</v>
       </c>
       <c r="X3" t="n">
-        <v>69265.83</v>
+        <v>52340.83</v>
       </c>
     </row>
     <row r="4">
@@ -3844,19 +3844,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1309.35</v>
+        <v>1206.97</v>
       </c>
       <c r="G4" t="n">
-        <v>42476.48</v>
+        <v>30097.61</v>
       </c>
       <c r="H4" t="n">
-        <v>57294.17</v>
+        <v>44812.92</v>
       </c>
       <c r="I4" t="n">
         <v>3000</v>
       </c>
       <c r="J4" t="n">
-        <v>57000</v>
+        <v>37000</v>
       </c>
       <c r="K4" t="n">
         <v>-1500</v>
@@ -3865,13 +3865,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-26643.33</v>
+        <v>-16405.83</v>
       </c>
       <c r="N4" t="n">
-        <v>31856.67</v>
+        <v>22094.17</v>
       </c>
       <c r="O4" t="n">
-        <v>31856.67</v>
+        <v>22094.17</v>
       </c>
       <c r="P4" t="n">
         <v>1500</v>
@@ -3892,13 +3892,13 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>2700</v>
+        <v>1350</v>
       </c>
       <c r="W4" t="n">
-        <v>2737.5</v>
+        <v>1368.75</v>
       </c>
       <c r="X4" t="n">
-        <v>57294.17</v>
+        <v>44812.92</v>
       </c>
     </row>
     <row r="5">
@@ -3918,19 +3918,19 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1964.02</v>
+        <v>1810.46</v>
       </c>
       <c r="G5" t="n">
-        <v>30095.98</v>
+        <v>22212.04</v>
       </c>
       <c r="H5" t="n">
-        <v>45322.5</v>
+        <v>37285</v>
       </c>
       <c r="I5" t="n">
         <v>3000</v>
       </c>
       <c r="J5" t="n">
-        <v>57000</v>
+        <v>37000</v>
       </c>
       <c r="K5" t="n">
         <v>-1500</v>
@@ -3939,13 +3939,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-39965</v>
+        <v>-24608.75</v>
       </c>
       <c r="N5" t="n">
-        <v>18535</v>
+        <v>13891.25</v>
       </c>
       <c r="O5" t="n">
-        <v>18535</v>
+        <v>13891.25</v>
       </c>
       <c r="P5" t="n">
         <v>1500</v>
@@ -3966,13 +3966,13 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>4050</v>
+        <v>2025</v>
       </c>
       <c r="W5" t="n">
-        <v>2737.5</v>
+        <v>1368.75</v>
       </c>
       <c r="X5" t="n">
-        <v>45322.5</v>
+        <v>37285</v>
       </c>
     </row>
     <row r="6">
@@ -3992,19 +3992,19 @@
         <v>12100</v>
       </c>
       <c r="F6" t="n">
-        <v>518.7</v>
+        <v>313.95</v>
       </c>
       <c r="G6" t="n">
-        <v>13665.47</v>
+        <v>12301.47</v>
       </c>
       <c r="H6" t="n">
-        <v>39300.83</v>
+        <v>37732.08</v>
       </c>
       <c r="I6" t="n">
         <v>3000</v>
       </c>
       <c r="J6" t="n">
-        <v>57000</v>
+        <v>37000</v>
       </c>
       <c r="K6" t="n">
         <v>-1500</v>
@@ -4013,13 +4013,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-53286.67</v>
+        <v>-32811.67</v>
       </c>
       <c r="N6" t="n">
-        <v>5213.33</v>
+        <v>5688.33</v>
       </c>
       <c r="O6" t="n">
-        <v>5213.33</v>
+        <v>5688.33</v>
       </c>
       <c r="P6" t="n">
         <v>1500</v>
@@ -4040,13 +4040,13 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1350</v>
+        <v>675</v>
       </c>
       <c r="W6" t="n">
-        <v>2737.5</v>
+        <v>1368.75</v>
       </c>
       <c r="X6" t="n">
-        <v>39300.83</v>
+        <v>37732.08</v>
       </c>
     </row>
     <row r="7">
@@ -4063,22 +4063,22 @@
         <v>1000</v>
       </c>
       <c r="E7" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>13384.96</v>
+        <v>16515.9</v>
       </c>
       <c r="H7" t="n">
-        <v>61850.79</v>
+        <v>65163.23</v>
       </c>
       <c r="I7" t="n">
         <v>3000</v>
       </c>
       <c r="J7" t="n">
-        <v>57000</v>
+        <v>37000</v>
       </c>
       <c r="K7" t="n">
         <v>-1500</v>
@@ -4087,13 +4087,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-44983.33</v>
+        <v>-19377.08</v>
       </c>
       <c r="N7" t="n">
-        <v>13516.67</v>
+        <v>19122.92</v>
       </c>
       <c r="O7" t="n">
-        <v>13516.67</v>
+        <v>19122.92</v>
       </c>
       <c r="P7" t="n">
         <v>1500</v>
@@ -4111,16 +4111,16 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>17875</v>
+        <v>18012.5</v>
       </c>
       <c r="V7" t="n">
-        <v>7721.62</v>
+        <v>6659.06</v>
       </c>
       <c r="W7" t="n">
-        <v>2737.5</v>
+        <v>1368.75</v>
       </c>
       <c r="X7" t="n">
-        <v>61850.79</v>
+        <v>65163.23</v>
       </c>
     </row>
     <row r="8">
@@ -4143,16 +4143,16 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>74509.45</v>
+        <v>76205.64</v>
       </c>
       <c r="H8" t="n">
-        <v>99134.45</v>
+        <v>100830.64</v>
       </c>
       <c r="I8" t="n">
         <v>3000</v>
       </c>
       <c r="J8" t="n">
-        <v>57000</v>
+        <v>37000</v>
       </c>
       <c r="K8" t="n">
         <v>-1500</v>
@@ -4161,19 +4161,19 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-56870</v>
+        <v>-31236.25</v>
       </c>
       <c r="N8" t="n">
-        <v>1630</v>
+        <v>7263.75</v>
       </c>
       <c r="O8" t="n">
-        <v>39630</v>
+        <v>42263.75</v>
       </c>
       <c r="P8" t="n">
         <v>1500</v>
       </c>
       <c r="Q8" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R8" t="n">
         <v>17500</v>
@@ -4185,16 +4185,16 @@
         <v>10000</v>
       </c>
       <c r="U8" t="n">
-        <v>16250</v>
+        <v>16375</v>
       </c>
       <c r="V8" t="n">
-        <v>10516.95</v>
+        <v>9454.389999999999</v>
       </c>
       <c r="W8" t="n">
         <v>2737.5</v>
       </c>
       <c r="X8" t="n">
-        <v>99134.45</v>
+        <v>100830.64</v>
       </c>
     </row>
     <row r="9">
@@ -4211,22 +4211,22 @@
         <v>1000</v>
       </c>
       <c r="E9" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>63711.99</v>
+        <v>66470.74000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>111686.16</v>
+        <v>114626.41</v>
       </c>
       <c r="I9" t="n">
         <v>3000</v>
       </c>
       <c r="J9" t="n">
-        <v>57000</v>
+        <v>37000</v>
       </c>
       <c r="K9" t="n">
         <v>-1500</v>
@@ -4235,40 +4235,40 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-47131.67</v>
+        <v>-21457.92</v>
       </c>
       <c r="N9" t="n">
-        <v>11368.33</v>
+        <v>17042.08</v>
       </c>
       <c r="O9" t="n">
-        <v>49368.33</v>
+        <v>52042.08</v>
       </c>
       <c r="P9" t="n">
         <v>1500</v>
       </c>
       <c r="Q9" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R9" t="n">
         <v>17083.33</v>
       </c>
       <c r="S9" t="n">
-        <v>3106.67</v>
+        <v>3091.67</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>32500</v>
+        <v>32750</v>
       </c>
       <c r="V9" t="n">
-        <v>6890.33</v>
+        <v>6921.83</v>
       </c>
       <c r="W9" t="n">
         <v>2737.5</v>
       </c>
       <c r="X9" t="n">
-        <v>111686.16</v>
+        <v>114626.41</v>
       </c>
     </row>
     <row r="10">
@@ -4291,16 +4291,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>87026.48</v>
+        <v>89966.73</v>
       </c>
       <c r="H10" t="n">
-        <v>111159.82</v>
+        <v>114100.07</v>
       </c>
       <c r="I10" t="n">
         <v>3000</v>
       </c>
       <c r="J10" t="n">
-        <v>57000</v>
+        <v>37000</v>
       </c>
       <c r="K10" t="n">
         <v>-1500</v>
@@ -4309,40 +4309,40 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-57393.33</v>
+        <v>-31679.58</v>
       </c>
       <c r="N10" t="n">
-        <v>1106.67</v>
+        <v>6820.42</v>
       </c>
       <c r="O10" t="n">
-        <v>39106.67</v>
+        <v>41820.42</v>
       </c>
       <c r="P10" t="n">
         <v>1500</v>
       </c>
       <c r="Q10" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R10" t="n">
         <v>16666.67</v>
       </c>
       <c r="S10" t="n">
-        <v>3713.33</v>
+        <v>3683.33</v>
       </c>
       <c r="T10" t="n">
         <v>10000</v>
       </c>
       <c r="U10" t="n">
-        <v>29250</v>
+        <v>29475</v>
       </c>
       <c r="V10" t="n">
-        <v>9685.65</v>
+        <v>9717.15</v>
       </c>
       <c r="W10" t="n">
         <v>2737.5</v>
       </c>
       <c r="X10" t="n">
-        <v>111159.82</v>
+        <v>114100.07</v>
       </c>
     </row>
     <row r="11">
@@ -4359,22 +4359,22 @@
         <v>1000</v>
       </c>
       <c r="E11" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>86175.98</v>
+        <v>89161.23</v>
       </c>
       <c r="H11" t="n">
-        <v>133658.48</v>
+        <v>136825.23</v>
       </c>
       <c r="I11" t="n">
         <v>3000</v>
       </c>
       <c r="J11" t="n">
-        <v>57000</v>
+        <v>37000</v>
       </c>
       <c r="K11" t="n">
         <v>-1500</v>
@@ -4383,19 +4383,19 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-46030</v>
+        <v>-20263.75</v>
       </c>
       <c r="N11" t="n">
-        <v>12470</v>
+        <v>18236.25</v>
       </c>
       <c r="O11" t="n">
-        <v>50470</v>
+        <v>53236.25</v>
       </c>
       <c r="P11" t="n">
         <v>1500</v>
       </c>
       <c r="Q11" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R11" t="n">
         <v>16250</v>
@@ -4407,16 +4407,16 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>43875</v>
+        <v>44212.5</v>
       </c>
       <c r="V11" t="n">
-        <v>16575.98</v>
+        <v>16638.98</v>
       </c>
       <c r="W11" t="n">
         <v>2737.5</v>
       </c>
       <c r="X11" t="n">
-        <v>133658.47</v>
+        <v>136825.23</v>
       </c>
     </row>
     <row r="12">
@@ -4439,16 +4439,16 @@
         <v>654.67</v>
       </c>
       <c r="G12" t="n">
-        <v>92914.49000000001</v>
+        <v>96018.24000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>105110.83</v>
+        <v>108214.58</v>
       </c>
       <c r="I12" t="n">
         <v>3000</v>
       </c>
       <c r="J12" t="n">
-        <v>57000</v>
+        <v>37000</v>
       </c>
       <c r="K12" t="n">
         <v>-1500</v>
@@ -4457,31 +4457,31 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-54666.67</v>
+        <v>-28847.92</v>
       </c>
       <c r="N12" t="n">
-        <v>3833.33</v>
+        <v>9652.08</v>
       </c>
       <c r="O12" t="n">
-        <v>41833.33</v>
+        <v>44652.08</v>
       </c>
       <c r="P12" t="n">
         <v>1500</v>
       </c>
       <c r="Q12" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R12" t="n">
         <v>15833.33</v>
       </c>
       <c r="S12" t="n">
-        <v>4356.67</v>
+        <v>4341.67</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>39000</v>
+        <v>39300</v>
       </c>
       <c r="V12" t="n">
         <v>1350</v>
@@ -4490,7 +4490,7 @@
         <v>2737.5</v>
       </c>
       <c r="X12" t="n">
-        <v>105110.83</v>
+        <v>108214.58</v>
       </c>
     </row>
     <row r="13">
@@ -4513,16 +4513,16 @@
         <v>1309.35</v>
       </c>
       <c r="G13" t="n">
-        <v>80533.98</v>
+        <v>83637.73</v>
       </c>
       <c r="H13" t="n">
-        <v>93139.17</v>
+        <v>96242.92</v>
       </c>
       <c r="I13" t="n">
         <v>3000</v>
       </c>
       <c r="J13" t="n">
-        <v>57000</v>
+        <v>37000</v>
       </c>
       <c r="K13" t="n">
         <v>-1500</v>
@@ -4531,31 +4531,31 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-63303.33</v>
+        <v>-37432.08</v>
       </c>
       <c r="N13" t="n">
-        <v>-4803.33</v>
+        <v>1067.92</v>
       </c>
       <c r="O13" t="n">
-        <v>33196.67</v>
+        <v>36067.92</v>
       </c>
       <c r="P13" t="n">
         <v>1500</v>
       </c>
       <c r="Q13" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R13" t="n">
         <v>15416.67</v>
       </c>
       <c r="S13" t="n">
-        <v>4963.33</v>
+        <v>4933.33</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>34125</v>
+        <v>34387.5</v>
       </c>
       <c r="V13" t="n">
         <v>2700</v>
@@ -4564,7 +4564,7 @@
         <v>2737.5</v>
       </c>
       <c r="X13" t="n">
-        <v>93139.17</v>
+        <v>96242.92</v>
       </c>
     </row>
     <row r="14">
@@ -4587,16 +4587,16 @@
         <v>2594.02</v>
       </c>
       <c r="G14" t="n">
-        <v>313953.47</v>
+        <v>317102.22</v>
       </c>
       <c r="H14" t="n">
-        <v>327597.5</v>
+        <v>330746.25</v>
       </c>
       <c r="I14" t="n">
         <v>4000</v>
       </c>
       <c r="J14" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K14" t="n">
         <v>-4500</v>
@@ -4605,19 +4605,19 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-71940</v>
+        <v>-46016.25</v>
       </c>
       <c r="N14" t="n">
-        <v>233560</v>
+        <v>239483.75</v>
       </c>
       <c r="O14" t="n">
-        <v>271560</v>
+        <v>274483.75</v>
       </c>
       <c r="P14" t="n">
         <v>2000</v>
       </c>
       <c r="Q14" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R14" t="n">
         <v>15000</v>
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>29250</v>
+        <v>29475</v>
       </c>
       <c r="V14" t="n">
         <v>4050</v>
@@ -4638,7 +4638,7 @@
         <v>2737.5</v>
       </c>
       <c r="X14" t="n">
-        <v>327597.5</v>
+        <v>330746.25</v>
       </c>
     </row>
     <row r="15">
@@ -4658,52 +4658,52 @@
         <v>12100</v>
       </c>
       <c r="F15" t="n">
-        <v>2271.72</v>
+        <v>2272.55</v>
       </c>
       <c r="G15" t="n">
-        <v>288681.41</v>
+        <v>291825.39</v>
       </c>
       <c r="H15" t="n">
-        <v>316311.46</v>
+        <v>319456.27</v>
       </c>
       <c r="I15" t="n">
         <v>4000</v>
       </c>
       <c r="J15" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K15" t="n">
         <v>-4500</v>
       </c>
       <c r="L15" t="n">
-        <v>-71940</v>
+        <v>-46016.25</v>
       </c>
       <c r="M15" t="n">
-        <v>-14846.87</v>
+        <v>-14798.31</v>
       </c>
       <c r="N15" t="n">
-        <v>218713.12</v>
+        <v>224685.44</v>
       </c>
       <c r="O15" t="n">
-        <v>256713.12</v>
+        <v>259685.44</v>
       </c>
       <c r="P15" t="n">
         <v>2000</v>
       </c>
       <c r="Q15" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R15" t="n">
         <v>14583.33</v>
       </c>
       <c r="S15" t="n">
-        <v>5190</v>
+        <v>5175</v>
       </c>
       <c r="T15" t="n">
         <v>10000</v>
       </c>
       <c r="U15" t="n">
-        <v>24375</v>
+        <v>24562.5</v>
       </c>
       <c r="V15" t="n">
         <v>1800</v>
@@ -4712,7 +4712,7 @@
         <v>3650</v>
       </c>
       <c r="X15" t="n">
-        <v>316311.46</v>
+        <v>319456.27</v>
       </c>
     </row>
     <row r="16">
@@ -4729,64 +4729,64 @@
         <v>1000</v>
       </c>
       <c r="E16" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>280257.64</v>
+        <v>283395.27</v>
       </c>
       <c r="H16" t="n">
-        <v>329910.97</v>
+        <v>333230.1</v>
       </c>
       <c r="I16" t="n">
         <v>4000</v>
       </c>
       <c r="J16" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K16" t="n">
         <v>-4500</v>
       </c>
       <c r="L16" t="n">
-        <v>-71940</v>
+        <v>-46016.25</v>
       </c>
       <c r="M16" t="n">
-        <v>-8245.450000000001</v>
+        <v>-8137.14</v>
       </c>
       <c r="N16" t="n">
-        <v>225314.55</v>
+        <v>231346.61</v>
       </c>
       <c r="O16" t="n">
-        <v>263314.55</v>
+        <v>266346.61</v>
       </c>
       <c r="P16" t="n">
         <v>2000</v>
       </c>
       <c r="Q16" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R16" t="n">
         <v>14166.67</v>
       </c>
       <c r="S16" t="n">
-        <v>5380</v>
+        <v>5350</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>37375</v>
+        <v>37662.5</v>
       </c>
       <c r="V16" t="n">
-        <v>6024.76</v>
+        <v>6054.33</v>
       </c>
       <c r="W16" t="n">
         <v>3650</v>
       </c>
       <c r="X16" t="n">
-        <v>329910.97</v>
+        <v>333230.1</v>
       </c>
     </row>
     <row r="17">
@@ -4809,37 +4809,37 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>296071.13</v>
+        <v>299428.91</v>
       </c>
       <c r="H17" t="n">
-        <v>321829.46</v>
+        <v>325187.24</v>
       </c>
       <c r="I17" t="n">
         <v>4000</v>
       </c>
       <c r="J17" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K17" t="n">
         <v>-4500</v>
       </c>
       <c r="L17" t="n">
-        <v>-71940</v>
+        <v>-46016.25</v>
       </c>
       <c r="M17" t="n">
-        <v>-21641.77</v>
+        <v>-21473.71</v>
       </c>
       <c r="N17" t="n">
-        <v>211918.23</v>
+        <v>218010.04</v>
       </c>
       <c r="O17" t="n">
-        <v>249918.23</v>
+        <v>253010.04</v>
       </c>
       <c r="P17" t="n">
         <v>2000</v>
       </c>
       <c r="Q17" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R17" t="n">
         <v>13750</v>
@@ -4851,16 +4851,16 @@
         <v>10000</v>
       </c>
       <c r="U17" t="n">
-        <v>30875</v>
+        <v>31112.5</v>
       </c>
       <c r="V17" t="n">
-        <v>8636.23</v>
+        <v>8664.700000000001</v>
       </c>
       <c r="W17" t="n">
         <v>3650</v>
       </c>
       <c r="X17" t="n">
-        <v>321829.46</v>
+        <v>325187.24</v>
       </c>
     </row>
     <row r="18">
@@ -4877,64 +4877,64 @@
         <v>1000</v>
       </c>
       <c r="E18" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>280019.19</v>
+        <v>283340.56</v>
       </c>
       <c r="H18" t="n">
-        <v>329072.52</v>
+        <v>332575.39</v>
       </c>
       <c r="I18" t="n">
         <v>4000</v>
       </c>
       <c r="J18" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K18" t="n">
         <v>-4500</v>
       </c>
       <c r="L18" t="n">
-        <v>-71940</v>
+        <v>-46016.25</v>
       </c>
       <c r="M18" t="n">
-        <v>-13581.46</v>
+        <v>-13342.46</v>
       </c>
       <c r="N18" t="n">
-        <v>219978.54</v>
+        <v>226141.29</v>
       </c>
       <c r="O18" t="n">
-        <v>257978.54</v>
+        <v>261141.29</v>
       </c>
       <c r="P18" t="n">
         <v>2000</v>
       </c>
       <c r="Q18" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R18" t="n">
         <v>13333.33</v>
       </c>
       <c r="S18" t="n">
-        <v>5190</v>
+        <v>5175</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>42250</v>
+        <v>42575</v>
       </c>
       <c r="V18" t="n">
-        <v>6670.64</v>
+        <v>6700.77</v>
       </c>
       <c r="W18" t="n">
         <v>3650</v>
       </c>
       <c r="X18" t="n">
-        <v>329072.52</v>
+        <v>332575.39</v>
       </c>
     </row>
     <row r="19">
@@ -4951,64 +4951,64 @@
         <v>1000</v>
       </c>
       <c r="E19" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>296200.73</v>
+        <v>299695.66</v>
       </c>
       <c r="H19" t="n">
-        <v>344954.07</v>
+        <v>348630.5</v>
       </c>
       <c r="I19" t="n">
         <v>4000</v>
       </c>
       <c r="J19" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K19" t="n">
         <v>-4500</v>
       </c>
       <c r="L19" t="n">
-        <v>-71940</v>
+        <v>-46016.25</v>
       </c>
       <c r="M19" t="n">
-        <v>-25518.89</v>
+        <v>-25208.95</v>
       </c>
       <c r="N19" t="n">
-        <v>208041.11</v>
+        <v>214274.8</v>
       </c>
       <c r="O19" t="n">
-        <v>246041.11</v>
+        <v>249274.8</v>
       </c>
       <c r="P19" t="n">
         <v>2000</v>
       </c>
       <c r="Q19" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R19" t="n">
         <v>12916.67</v>
       </c>
       <c r="S19" t="n">
-        <v>5380</v>
+        <v>5350</v>
       </c>
       <c r="T19" t="n">
         <v>10000</v>
       </c>
       <c r="U19" t="n">
-        <v>53625</v>
+        <v>54037.5</v>
       </c>
       <c r="V19" t="n">
-        <v>13341.29</v>
+        <v>13401.53</v>
       </c>
       <c r="W19" t="n">
         <v>3650</v>
       </c>
       <c r="X19" t="n">
-        <v>344954.07</v>
+        <v>348630.5</v>
       </c>
     </row>
     <row r="20">
@@ -5025,43 +5025,43 @@
         <v>1000</v>
       </c>
       <c r="E20" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>311608.08</v>
+        <v>315319.98</v>
       </c>
       <c r="H20" t="n">
-        <v>360061.41</v>
+        <v>363954.81</v>
       </c>
       <c r="I20" t="n">
         <v>4000</v>
       </c>
       <c r="J20" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K20" t="n">
         <v>-4500</v>
       </c>
       <c r="L20" t="n">
-        <v>-71940</v>
+        <v>-46016.25</v>
       </c>
       <c r="M20" t="n">
-        <v>-15999.69</v>
+        <v>-15607.62</v>
       </c>
       <c r="N20" t="n">
-        <v>217560.31</v>
+        <v>223876.12</v>
       </c>
       <c r="O20" t="n">
-        <v>255560.31</v>
+        <v>258876.12</v>
       </c>
       <c r="P20" t="n">
         <v>2000</v>
       </c>
       <c r="Q20" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R20" t="n">
         <v>12500</v>
@@ -5073,16 +5073,16 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>63375</v>
+        <v>63862.5</v>
       </c>
       <c r="V20" t="n">
-        <v>19976.1</v>
+        <v>20066.19</v>
       </c>
       <c r="W20" t="n">
         <v>3650</v>
       </c>
       <c r="X20" t="n">
-        <v>360061.41</v>
+        <v>363954.82</v>
       </c>
     </row>
     <row r="21">
@@ -5099,64 +5099,64 @@
         <v>1000</v>
       </c>
       <c r="E21" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>307611.58</v>
+        <v>311405.37</v>
       </c>
       <c r="H21" t="n">
-        <v>355764.92</v>
+        <v>359740.2</v>
       </c>
       <c r="I21" t="n">
         <v>4000</v>
       </c>
       <c r="J21" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K21" t="n">
         <v>-4500</v>
       </c>
       <c r="L21" t="n">
-        <v>-71940</v>
+        <v>-46016.25</v>
       </c>
       <c r="M21" t="n">
-        <v>-26478.23</v>
+        <v>-26004.04</v>
       </c>
       <c r="N21" t="n">
-        <v>207081.77</v>
+        <v>213479.71</v>
       </c>
       <c r="O21" t="n">
-        <v>245081.77</v>
+        <v>248479.71</v>
       </c>
       <c r="P21" t="n">
         <v>2000</v>
       </c>
       <c r="Q21" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R21" t="n">
         <v>12083.33</v>
       </c>
       <c r="S21" t="n">
-        <v>5190</v>
+        <v>5175</v>
       </c>
       <c r="T21" t="n">
         <v>10000</v>
       </c>
       <c r="U21" t="n">
-        <v>73125</v>
+        <v>73687.5</v>
       </c>
       <c r="V21" t="n">
-        <v>6634.81</v>
+        <v>6664.66</v>
       </c>
       <c r="W21" t="n">
         <v>3650</v>
       </c>
       <c r="X21" t="n">
-        <v>355764.92</v>
+        <v>359740.2</v>
       </c>
     </row>
     <row r="22">
@@ -5173,64 +5173,64 @@
         <v>1000</v>
       </c>
       <c r="E22" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>323386.99</v>
+        <v>327351.16</v>
       </c>
       <c r="H22" t="n">
-        <v>371240.32</v>
+        <v>375385.99</v>
       </c>
       <c r="I22" t="n">
         <v>4000</v>
       </c>
       <c r="J22" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K22" t="n">
         <v>-4500</v>
       </c>
       <c r="L22" t="n">
-        <v>-71940</v>
+        <v>-46016.25</v>
       </c>
       <c r="M22" t="n">
-        <v>-15500.14</v>
+        <v>-14932.64</v>
       </c>
       <c r="N22" t="n">
-        <v>218059.86</v>
+        <v>224551.11</v>
       </c>
       <c r="O22" t="n">
-        <v>256059.86</v>
+        <v>259551.11</v>
       </c>
       <c r="P22" t="n">
         <v>2000</v>
       </c>
       <c r="Q22" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="R22" t="n">
         <v>11666.67</v>
       </c>
       <c r="S22" t="n">
-        <v>5380</v>
+        <v>5350</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>81250</v>
+        <v>81875</v>
       </c>
       <c r="V22" t="n">
-        <v>13233.79</v>
+        <v>13293.21</v>
       </c>
       <c r="W22" t="n">
         <v>3650</v>
       </c>
       <c r="X22" t="n">
-        <v>371240.32</v>
+        <v>375385.99</v>
       </c>
     </row>
     <row r="23">
@@ -5253,58 +5253,58 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>338801.11</v>
+        <v>342982.24</v>
       </c>
       <c r="H23" t="n">
-        <v>362759.44</v>
+        <v>366940.58</v>
       </c>
       <c r="I23" t="n">
         <v>4000</v>
       </c>
       <c r="J23" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K23" t="n">
         <v>-4500</v>
       </c>
       <c r="L23" t="n">
-        <v>-71940</v>
+        <v>-46016.25</v>
       </c>
       <c r="M23" t="n">
-        <v>-25974.17</v>
+        <v>-25324.54</v>
       </c>
       <c r="N23" t="n">
-        <v>207585.83</v>
+        <v>214159.21</v>
       </c>
       <c r="O23" t="n">
-        <v>245585.83</v>
+        <v>249159.21</v>
       </c>
       <c r="P23" t="n">
         <v>2000</v>
       </c>
       <c r="Q23" t="n">
-        <v>36100</v>
+        <v>33250</v>
       </c>
       <c r="R23" t="n">
         <v>11250</v>
       </c>
       <c r="S23" t="n">
-        <v>6900</v>
+        <v>6750</v>
       </c>
       <c r="T23" t="n">
         <v>10000</v>
       </c>
       <c r="U23" t="n">
-        <v>71500</v>
+        <v>72050</v>
       </c>
       <c r="V23" t="n">
-        <v>15773.61</v>
+        <v>15831.37</v>
       </c>
       <c r="W23" t="n">
         <v>3650</v>
       </c>
       <c r="X23" t="n">
-        <v>362759.44</v>
+        <v>366940.58</v>
       </c>
     </row>
     <row r="24">
@@ -5321,64 +5321,64 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>315212.42</v>
+        <v>319324.68</v>
       </c>
       <c r="H24" t="n">
-        <v>362465.75</v>
+        <v>366759.51</v>
       </c>
       <c r="I24" t="n">
         <v>4000</v>
       </c>
       <c r="J24" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K24" t="n">
         <v>-4500</v>
       </c>
       <c r="L24" t="n">
-        <v>-71940</v>
+        <v>-46016.25</v>
       </c>
       <c r="M24" t="n">
-        <v>-14991.56</v>
+        <v>-14248.62</v>
       </c>
       <c r="N24" t="n">
-        <v>218568.44</v>
+        <v>225235.13</v>
       </c>
       <c r="O24" t="n">
-        <v>256568.44</v>
+        <v>260235.13</v>
       </c>
       <c r="P24" t="n">
         <v>2000</v>
       </c>
       <c r="Q24" t="n">
-        <v>36100</v>
+        <v>33250</v>
       </c>
       <c r="R24" t="n">
         <v>10833.33</v>
       </c>
       <c r="S24" t="n">
-        <v>7090</v>
+        <v>6925</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>79625</v>
+        <v>80237.5</v>
       </c>
       <c r="V24" t="n">
-        <v>6598.98</v>
+        <v>6628.55</v>
       </c>
       <c r="W24" t="n">
         <v>3650</v>
       </c>
       <c r="X24" t="n">
-        <v>362465.75</v>
+        <v>366759.51</v>
       </c>
     </row>
     <row r="25">
@@ -5401,58 +5401,58 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>330994.59</v>
+        <v>335277.24</v>
       </c>
       <c r="H25" t="n">
-        <v>354352.93</v>
+        <v>358635.57</v>
       </c>
       <c r="I25" t="n">
         <v>4000</v>
       </c>
       <c r="J25" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K25" t="n">
         <v>-4500</v>
       </c>
       <c r="L25" t="n">
-        <v>-71940</v>
+        <v>-46016.25</v>
       </c>
       <c r="M25" t="n">
-        <v>-24006.7</v>
+        <v>-23170.45</v>
       </c>
       <c r="N25" t="n">
-        <v>209553.3</v>
+        <v>216313.3</v>
       </c>
       <c r="O25" t="n">
-        <v>247553.3</v>
+        <v>251313.3</v>
       </c>
       <c r="P25" t="n">
         <v>2000</v>
       </c>
       <c r="Q25" t="n">
-        <v>36100</v>
+        <v>33250</v>
       </c>
       <c r="R25" t="n">
         <v>10416.67</v>
       </c>
       <c r="S25" t="n">
-        <v>7280</v>
+        <v>7100</v>
       </c>
       <c r="T25" t="n">
         <v>10000</v>
       </c>
       <c r="U25" t="n">
-        <v>68250</v>
+        <v>68775</v>
       </c>
       <c r="V25" t="n">
-        <v>9102.959999999999</v>
+        <v>9130.6</v>
       </c>
       <c r="W25" t="n">
         <v>3650</v>
       </c>
       <c r="X25" t="n">
-        <v>354352.93</v>
+        <v>358635.57</v>
       </c>
     </row>
     <row r="26">
@@ -5469,64 +5469,64 @@
         <v>1000</v>
       </c>
       <c r="E26" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>322407.57</v>
+        <v>326722.51</v>
       </c>
       <c r="H26" t="n">
-        <v>369060.9</v>
+        <v>373557.34</v>
       </c>
       <c r="I26" t="n">
         <v>4000</v>
       </c>
       <c r="J26" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K26" t="n">
         <v>-4500</v>
       </c>
       <c r="L26" t="n">
-        <v>-71940</v>
+        <v>-46016.25</v>
       </c>
       <c r="M26" t="n">
-        <v>-11565.21</v>
+        <v>-10624.46</v>
       </c>
       <c r="N26" t="n">
-        <v>221994.79</v>
+        <v>228859.29</v>
       </c>
       <c r="O26" t="n">
-        <v>259994.79</v>
+        <v>263859.29</v>
       </c>
       <c r="P26" t="n">
         <v>2000</v>
       </c>
       <c r="Q26" t="n">
-        <v>34200</v>
+        <v>31500</v>
       </c>
       <c r="R26" t="n">
         <v>10000</v>
       </c>
       <c r="S26" t="n">
-        <v>8800</v>
+        <v>8500</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>74750</v>
+        <v>75325</v>
       </c>
       <c r="V26" t="n">
-        <v>15666.11</v>
+        <v>15723.05</v>
       </c>
       <c r="W26" t="n">
         <v>3650</v>
       </c>
       <c r="X26" t="n">
-        <v>369060.9</v>
+        <v>373557.34</v>
       </c>
     </row>
     <row r="27">
@@ -5546,52 +5546,52 @@
         <v>12100</v>
       </c>
       <c r="F27" t="n">
-        <v>243.25</v>
+        <v>245.45</v>
       </c>
       <c r="G27" t="n">
-        <v>314805.29</v>
+        <v>319232.09</v>
       </c>
       <c r="H27" t="n">
-        <v>340261.04</v>
+        <v>344690.04</v>
       </c>
       <c r="I27" t="n">
         <v>4000</v>
       </c>
       <c r="J27" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K27" t="n">
         <v>-4500</v>
       </c>
       <c r="L27" t="n">
-        <v>-83505.21000000001</v>
+        <v>-56640.71</v>
       </c>
       <c r="M27" t="n">
-        <v>-13342.08</v>
+        <v>-13237.58</v>
       </c>
       <c r="N27" t="n">
-        <v>208652.71</v>
+        <v>215621.71</v>
       </c>
       <c r="O27" t="n">
-        <v>246652.71</v>
+        <v>250621.71</v>
       </c>
       <c r="P27" t="n">
         <v>2000</v>
       </c>
       <c r="Q27" t="n">
-        <v>34200</v>
+        <v>31500</v>
       </c>
       <c r="R27" t="n">
         <v>9583.33</v>
       </c>
       <c r="S27" t="n">
-        <v>8990</v>
+        <v>8675</v>
       </c>
       <c r="T27" t="n">
         <v>10000</v>
       </c>
       <c r="U27" t="n">
-        <v>61750</v>
+        <v>62225</v>
       </c>
       <c r="V27" t="n">
         <v>2340</v>
@@ -5600,7 +5600,7 @@
         <v>4745</v>
       </c>
       <c r="X27" t="n">
-        <v>340261.04</v>
+        <v>344690.04</v>
       </c>
     </row>
     <row r="28">
@@ -5617,64 +5617,64 @@
         <v>1000</v>
       </c>
       <c r="E28" t="n">
-        <v>47795</v>
+        <v>47976.5</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>301206.38</v>
+        <v>305620.47</v>
       </c>
       <c r="H28" t="n">
-        <v>361768.05</v>
+        <v>366363.64</v>
       </c>
       <c r="I28" t="n">
         <v>4000</v>
       </c>
       <c r="J28" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K28" t="n">
         <v>-4500</v>
       </c>
       <c r="L28" t="n">
-        <v>-83505.21000000001</v>
+        <v>-56640.71</v>
       </c>
       <c r="M28" t="n">
-        <v>-6681.91</v>
+        <v>-6472.91</v>
       </c>
       <c r="N28" t="n">
-        <v>215312.88</v>
+        <v>222386.38</v>
       </c>
       <c r="O28" t="n">
-        <v>253312.88</v>
+        <v>257386.38</v>
       </c>
       <c r="P28" t="n">
         <v>2000</v>
       </c>
       <c r="Q28" t="n">
-        <v>34200</v>
+        <v>31500</v>
       </c>
       <c r="R28" t="n">
         <v>9166.67</v>
       </c>
       <c r="S28" t="n">
-        <v>9180</v>
+        <v>8850</v>
       </c>
       <c r="T28" t="n">
         <v>10000</v>
       </c>
       <c r="U28" t="n">
-        <v>68250</v>
+        <v>68775</v>
       </c>
       <c r="V28" t="n">
-        <v>10913.5</v>
+        <v>10940.59</v>
       </c>
       <c r="W28" t="n">
         <v>4745</v>
       </c>
       <c r="X28" t="n">
-        <v>361768.05</v>
+        <v>366363.64</v>
       </c>
     </row>
     <row r="29">
@@ -5691,64 +5691,64 @@
         <v>1000</v>
       </c>
       <c r="E29" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>322528.27</v>
+        <v>327154.57</v>
       </c>
       <c r="H29" t="n">
-        <v>370644.11</v>
+        <v>375451.9</v>
       </c>
       <c r="I29" t="n">
         <v>4000</v>
       </c>
       <c r="J29" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K29" t="n">
         <v>-4500</v>
       </c>
       <c r="L29" t="n">
-        <v>-83505.21000000001</v>
+        <v>-56640.71</v>
       </c>
       <c r="M29" t="n">
-        <v>1434.9</v>
+        <v>1759.58</v>
       </c>
       <c r="N29" t="n">
-        <v>223429.69</v>
+        <v>230618.88</v>
       </c>
       <c r="O29" t="n">
-        <v>261429.69</v>
+        <v>265618.88</v>
       </c>
       <c r="P29" t="n">
         <v>2000</v>
       </c>
       <c r="Q29" t="n">
-        <v>32300</v>
+        <v>29750</v>
       </c>
       <c r="R29" t="n">
         <v>8750</v>
       </c>
       <c r="S29" t="n">
-        <v>10700</v>
+        <v>10250</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>73125</v>
+        <v>73687.5</v>
       </c>
       <c r="V29" t="n">
-        <v>17594.42</v>
+        <v>17650.53</v>
       </c>
       <c r="W29" t="n">
         <v>4745</v>
       </c>
       <c r="X29" t="n">
-        <v>370644.11</v>
+        <v>375451.9</v>
       </c>
     </row>
     <row r="30">
@@ -5765,64 +5765,64 @@
         <v>1000</v>
       </c>
       <c r="E30" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>314728</v>
+        <v>319465.4</v>
       </c>
       <c r="H30" t="n">
-        <v>362498</v>
+        <v>367416.9</v>
       </c>
       <c r="I30" t="n">
         <v>4000</v>
       </c>
       <c r="J30" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K30" t="n">
         <v>-4500</v>
       </c>
       <c r="L30" t="n">
-        <v>-83505.21000000001</v>
+        <v>-56640.71</v>
       </c>
       <c r="M30" t="n">
-        <v>-10446.04</v>
+        <v>-10005.67</v>
       </c>
       <c r="N30" t="n">
-        <v>211548.75</v>
+        <v>218853.62</v>
       </c>
       <c r="O30" t="n">
-        <v>249548.75</v>
+        <v>253853.62</v>
       </c>
       <c r="P30" t="n">
         <v>2000</v>
       </c>
       <c r="Q30" t="n">
-        <v>32300</v>
+        <v>29750</v>
       </c>
       <c r="R30" t="n">
         <v>8333.33</v>
       </c>
       <c r="S30" t="n">
-        <v>10890</v>
+        <v>10425</v>
       </c>
       <c r="T30" t="n">
         <v>10000</v>
       </c>
       <c r="U30" t="n">
-        <v>78000</v>
+        <v>78600</v>
       </c>
       <c r="V30" t="n">
-        <v>6680.92</v>
+        <v>6709.94</v>
       </c>
       <c r="W30" t="n">
         <v>4745</v>
       </c>
       <c r="X30" t="n">
-        <v>362498</v>
+        <v>367416.9</v>
       </c>
     </row>
     <row r="31">
@@ -5839,64 +5839,64 @@
         <v>1000</v>
       </c>
       <c r="E31" t="n">
-        <v>71390</v>
+        <v>71753</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>324317.95</v>
+        <v>329220.96</v>
       </c>
       <c r="H31" t="n">
-        <v>407437.12</v>
+        <v>412703.13</v>
       </c>
       <c r="I31" t="n">
         <v>4000</v>
       </c>
       <c r="J31" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K31" t="n">
         <v>-4500</v>
       </c>
       <c r="L31" t="n">
-        <v>-83505.21000000001</v>
+        <v>-56640.71</v>
       </c>
       <c r="M31" t="n">
-        <v>-870.35</v>
+        <v>-303.1</v>
       </c>
       <c r="N31" t="n">
-        <v>221124.44</v>
+        <v>228556.19</v>
       </c>
       <c r="O31" t="n">
-        <v>259124.44</v>
+        <v>263556.19</v>
       </c>
       <c r="P31" t="n">
         <v>2000</v>
       </c>
       <c r="Q31" t="n">
-        <v>32300</v>
+        <v>29750</v>
       </c>
       <c r="R31" t="n">
         <v>7916.67</v>
       </c>
       <c r="S31" t="n">
-        <v>11080</v>
+        <v>10600</v>
       </c>
       <c r="T31" t="n">
         <v>10000</v>
       </c>
       <c r="U31" t="n">
-        <v>100750</v>
+        <v>101525</v>
       </c>
       <c r="V31" t="n">
-        <v>19521.01</v>
+        <v>19610.27</v>
       </c>
       <c r="W31" t="n">
         <v>4745</v>
       </c>
       <c r="X31" t="n">
-        <v>407437.12</v>
+        <v>412703.13</v>
       </c>
     </row>
     <row r="32">
@@ -5913,64 +5913,64 @@
         <v>1000</v>
       </c>
       <c r="E32" t="n">
-        <v>59290</v>
+        <v>59653</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>368828.7</v>
+        <v>374122.24</v>
       </c>
       <c r="H32" t="n">
-        <v>439502.03</v>
+        <v>445158.58</v>
       </c>
       <c r="I32" t="n">
         <v>4000</v>
       </c>
       <c r="J32" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K32" t="n">
         <v>-4500</v>
       </c>
       <c r="L32" t="n">
-        <v>-83505.21000000001</v>
+        <v>-56640.71</v>
       </c>
       <c r="M32" t="n">
-        <v>10161.98</v>
+        <v>10867.29</v>
       </c>
       <c r="N32" t="n">
-        <v>232156.77</v>
+        <v>239726.58</v>
       </c>
       <c r="O32" t="n">
-        <v>270156.77</v>
+        <v>274726.58</v>
       </c>
       <c r="P32" t="n">
         <v>2000</v>
       </c>
       <c r="Q32" t="n">
-        <v>30400</v>
+        <v>28000</v>
       </c>
       <c r="R32" t="n">
         <v>7500</v>
       </c>
       <c r="S32" t="n">
-        <v>12600</v>
+        <v>12000</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>121875</v>
+        <v>122812.5</v>
       </c>
       <c r="V32" t="n">
-        <v>30225.26</v>
+        <v>30374.49</v>
       </c>
       <c r="W32" t="n">
         <v>4745</v>
       </c>
       <c r="X32" t="n">
-        <v>439502.03</v>
+        <v>445158.58</v>
       </c>
     </row>
     <row r="33">
@@ -5987,64 +5987,64 @@
         <v>1000</v>
       </c>
       <c r="E33" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>371586.44</v>
+        <v>377076.29</v>
       </c>
       <c r="H33" t="n">
-        <v>418318.94</v>
+        <v>423990.29</v>
       </c>
       <c r="I33" t="n">
         <v>4000</v>
       </c>
       <c r="J33" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K33" t="n">
         <v>-4500</v>
       </c>
       <c r="L33" t="n">
-        <v>-83505.21000000001</v>
+        <v>-56640.71</v>
       </c>
       <c r="M33" t="n">
-        <v>1196.56</v>
+        <v>2039.94</v>
       </c>
       <c r="N33" t="n">
-        <v>223191.35</v>
+        <v>230899.23</v>
       </c>
       <c r="O33" t="n">
-        <v>261191.35</v>
+        <v>265899.23</v>
       </c>
       <c r="P33" t="n">
         <v>2000</v>
       </c>
       <c r="Q33" t="n">
-        <v>30400</v>
+        <v>28000</v>
       </c>
       <c r="R33" t="n">
         <v>7083.33</v>
       </c>
       <c r="S33" t="n">
-        <v>12790</v>
+        <v>12175</v>
       </c>
       <c r="T33" t="n">
         <v>10000</v>
       </c>
       <c r="U33" t="n">
-        <v>123500</v>
+        <v>124450</v>
       </c>
       <c r="V33" t="n">
-        <v>6609.26</v>
+        <v>6637.72</v>
       </c>
       <c r="W33" t="n">
         <v>4745</v>
       </c>
       <c r="X33" t="n">
-        <v>418318.94</v>
+        <v>423990.29</v>
       </c>
     </row>
     <row r="34">
@@ -6061,64 +6061,64 @@
         <v>1000</v>
       </c>
       <c r="E34" t="n">
-        <v>71390</v>
+        <v>71753</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>380770.25</v>
+        <v>386422.54</v>
       </c>
       <c r="H34" t="n">
-        <v>462851.92</v>
+        <v>468867.2</v>
       </c>
       <c r="I34" t="n">
         <v>4000</v>
       </c>
       <c r="J34" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K34" t="n">
         <v>-4500</v>
       </c>
       <c r="L34" t="n">
-        <v>-83505.21000000001</v>
+        <v>-56640.71</v>
       </c>
       <c r="M34" t="n">
-        <v>13687.78</v>
+        <v>14680.4</v>
       </c>
       <c r="N34" t="n">
-        <v>235682.57</v>
+        <v>243539.69</v>
       </c>
       <c r="O34" t="n">
-        <v>273682.57</v>
+        <v>278539.69</v>
       </c>
       <c r="P34" t="n">
         <v>2000</v>
       </c>
       <c r="Q34" t="n">
-        <v>30400</v>
+        <v>28000</v>
       </c>
       <c r="R34" t="n">
         <v>6666.67</v>
       </c>
       <c r="S34" t="n">
-        <v>12980</v>
+        <v>12350</v>
       </c>
       <c r="T34" t="n">
         <v>10000</v>
       </c>
       <c r="U34" t="n">
-        <v>143000</v>
+        <v>144100</v>
       </c>
       <c r="V34" t="n">
-        <v>19377.68</v>
+        <v>19465.84</v>
       </c>
       <c r="W34" t="n">
         <v>4745</v>
       </c>
       <c r="X34" t="n">
-        <v>462851.92</v>
+        <v>468867.2</v>
       </c>
     </row>
     <row r="35">
@@ -6135,64 +6135,64 @@
         <v>1000</v>
       </c>
       <c r="E35" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>422974.86</v>
+        <v>429164.5</v>
       </c>
       <c r="H35" t="n">
-        <v>469015.69</v>
+        <v>475386.83</v>
       </c>
       <c r="I35" t="n">
         <v>4000</v>
       </c>
       <c r="J35" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K35" t="n">
         <v>-4500</v>
       </c>
       <c r="L35" t="n">
-        <v>-83505.21000000001</v>
+        <v>-56640.71</v>
       </c>
       <c r="M35" t="n">
-        <v>27635.62</v>
+        <v>28788.69</v>
       </c>
       <c r="N35" t="n">
-        <v>249630.42</v>
+        <v>257647.98</v>
       </c>
       <c r="O35" t="n">
-        <v>285730.42</v>
+        <v>290897.98</v>
       </c>
       <c r="P35" t="n">
         <v>2000</v>
       </c>
       <c r="Q35" t="n">
-        <v>28500</v>
+        <v>26250</v>
       </c>
       <c r="R35" t="n">
         <v>6250</v>
       </c>
       <c r="S35" t="n">
-        <v>12600</v>
+        <v>12000</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>141375</v>
+        <v>142462.5</v>
       </c>
       <c r="V35" t="n">
-        <v>25915.27</v>
+        <v>26031.35</v>
       </c>
       <c r="W35" t="n">
         <v>4745</v>
       </c>
       <c r="X35" t="n">
-        <v>469015.69</v>
+        <v>475386.83</v>
       </c>
     </row>
     <row r="36">
@@ -6209,64 +6209,64 @@
         <v>1000</v>
       </c>
       <c r="E36" t="n">
-        <v>35695</v>
+        <v>35876.5</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>406041.45</v>
+        <v>412275.86</v>
       </c>
       <c r="H36" t="n">
-        <v>451736.45</v>
+        <v>458152.36</v>
       </c>
       <c r="I36" t="n">
         <v>4000</v>
       </c>
       <c r="J36" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K36" t="n">
         <v>-4500</v>
       </c>
       <c r="L36" t="n">
-        <v>-83505.21000000001</v>
+        <v>-56640.71</v>
       </c>
       <c r="M36" t="n">
-        <v>21595.23</v>
+        <v>22907.98</v>
       </c>
       <c r="N36" t="n">
-        <v>243590.02</v>
+        <v>251767.27</v>
       </c>
       <c r="O36" t="n">
-        <v>279690.02</v>
+        <v>285017.27</v>
       </c>
       <c r="P36" t="n">
         <v>2000</v>
       </c>
       <c r="Q36" t="n">
-        <v>28500</v>
+        <v>26250</v>
       </c>
       <c r="R36" t="n">
         <v>5833.33</v>
       </c>
       <c r="S36" t="n">
-        <v>12780.5</v>
+        <v>12166.25</v>
       </c>
       <c r="T36" t="n">
         <v>10000</v>
       </c>
       <c r="U36" t="n">
-        <v>139750</v>
+        <v>140825</v>
       </c>
       <c r="V36" t="n">
-        <v>6537.59</v>
+        <v>6565.51</v>
       </c>
       <c r="W36" t="n">
         <v>4745</v>
       </c>
       <c r="X36" t="n">
-        <v>451736.45</v>
+        <v>458152.36</v>
       </c>
     </row>
     <row r="37">
@@ -6283,64 +6283,64 @@
         <v>1000</v>
       </c>
       <c r="E37" t="n">
-        <v>47795</v>
+        <v>47976.5</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>414819.11</v>
+        <v>421212.8</v>
       </c>
       <c r="H37" t="n">
-        <v>472268.28</v>
+        <v>478843.46</v>
       </c>
       <c r="I37" t="n">
         <v>4000</v>
       </c>
       <c r="J37" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K37" t="n">
         <v>-4500</v>
       </c>
       <c r="L37" t="n">
-        <v>-83505.21000000001</v>
+        <v>-56640.71</v>
       </c>
       <c r="M37" t="n">
-        <v>37011.47</v>
+        <v>38495.09</v>
       </c>
       <c r="N37" t="n">
-        <v>259006.26</v>
+        <v>267354.38</v>
       </c>
       <c r="O37" t="n">
-        <v>295106.26</v>
+        <v>300604.38</v>
       </c>
       <c r="P37" t="n">
         <v>2000</v>
       </c>
       <c r="Q37" t="n">
-        <v>28500</v>
+        <v>26250</v>
       </c>
       <c r="R37" t="n">
         <v>5416.67</v>
       </c>
       <c r="S37" t="n">
-        <v>12961</v>
+        <v>12332.5</v>
       </c>
       <c r="T37" t="n">
         <v>10000</v>
       </c>
       <c r="U37" t="n">
-        <v>136500</v>
+        <v>137550</v>
       </c>
       <c r="V37" t="n">
-        <v>15139.36</v>
+        <v>15194.91</v>
       </c>
       <c r="W37" t="n">
         <v>4745</v>
       </c>
       <c r="X37" t="n">
-        <v>472268.28</v>
+        <v>478843.46</v>
       </c>
     </row>
     <row r="38">
@@ -6357,64 +6357,64 @@
         <v>1000</v>
       </c>
       <c r="E38" t="n">
-        <v>59290</v>
+        <v>59653</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>433051.08</v>
+        <v>439795.19</v>
       </c>
       <c r="H38" t="n">
-        <v>501649.41</v>
+        <v>508756.52</v>
       </c>
       <c r="I38" t="n">
         <v>4000</v>
       </c>
       <c r="J38" t="n">
-        <v>306000</v>
+        <v>286000</v>
       </c>
       <c r="K38" t="n">
         <v>-4500</v>
       </c>
       <c r="L38" t="n">
-        <v>-83505.21000000001</v>
+        <v>-56640.71</v>
       </c>
       <c r="M38" t="n">
-        <v>53884.33</v>
+        <v>55550.02</v>
       </c>
       <c r="N38" t="n">
-        <v>275879.12</v>
+        <v>284409.31</v>
       </c>
       <c r="O38" t="n">
-        <v>310079.12</v>
+        <v>315909.31</v>
       </c>
       <c r="P38" t="n">
         <v>2000</v>
       </c>
       <c r="Q38" t="n">
-        <v>26600</v>
+        <v>24500</v>
       </c>
       <c r="R38" t="n">
         <v>5000</v>
       </c>
       <c r="S38" t="n">
-        <v>12600</v>
+        <v>12000</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>151125</v>
+        <v>152287.5</v>
       </c>
       <c r="V38" t="n">
-        <v>25700.29</v>
+        <v>25814.71</v>
       </c>
       <c r="W38" t="n">
         <v>4745</v>
       </c>
       <c r="X38" t="n">
-        <v>501649.41</v>
+        <v>508756.52</v>
       </c>
     </row>
   </sheetData>
@@ -6428,7 +6428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19500.0</t>
+          <t>19650.0</t>
         </is>
       </c>
     </row>
@@ -6542,274 +6542,286 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cargas_sociales</t>
+          <t>recortes_fundadores</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>[[1, 5, 0.5]]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ss_trabajador</t>
+          <t>cargas_sociales</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>retencion_irpf</t>
+          <t>ss_trabajador</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.065</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gastos_anuales</t>
+          <t>retencion_irpf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{"Nube (cómputo, almacenamiento, demos)": [7200.0, 9600.0, 12000.0], "Asesoría jurídica": [4000.0, 8000.0, 6000.0], "Gestoría": [2400.0, 3600.0, 4800.0], "Actividad comercial y ferias": [5000.0, 15000.0, 25000.0], "Equipos menores, viajes y otros": [3000.0, 6000.0, 9000.0], "Seguros (responsabilidad civil)": [1200.0, 2000.0, 2000.0]}</t>
+          <t>0.18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>herramientas_persona_mes</t>
+          <t>gastos_anuales</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>{"Nube (cómputo, almacenamiento, demos)": [7200.0, 9600.0, 12000.0], "Asesoría jurídica": [4000.0, 8000.0, 6000.0], "Gestoría": [2400.0, 3600.0, 4800.0], "Actividad comercial y ferias": [5000.0, 15000.0, 25000.0], "Equipos menores, viajes y otros": [3000.0, 6000.0, 9000.0], "Seguros (responsabilidad civil)": [1200.0, 2000.0, 2000.0]}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>coworking_persona_mes</t>
+          <t>herramientas_persona_mes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>100.0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>comision_socio</t>
+          <t>coworking_persona_mes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>250.0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>comision_desde_mes</t>
+          <t>comision_socio</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>imprevistos</t>
+          <t>comision_desde_mes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>inversiones</t>
+          <t>imprevistos</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[13, "Equipo del ingeniero", 2500.0, "equipo"], [14, "Marca en la EUIPO", 1000.0, "marca"], [25, "Equipo del responsable comercial", 2500.0, "equipo"]]</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>amortizacion</t>
+          <t>inversiones</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{"marca": 0.1, "aplicaciones": 0.25, "mobiliario": 0.1, "equipo": 0.25}</t>
+          <t>[[13, "Equipo del ingeniero", 2500.0, "equipo"], [14, "Marca en la EUIPO", 1000.0, "marca"], [25, "Equipo del responsable comercial", 2500.0, "equipo"]]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>reparto_equipo</t>
+          <t>amortizacion</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{"equipo": 0.8, "mobiliario": 0.2}</t>
+          <t>{"marca": 0.1, "aplicaciones": 0.25, "mobiliario": 0.1, "equipo": 0.25}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>activo_inicial</t>
+          <t>reparto_equipo</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{"marca": 500.0, "aplicaciones": 5000.0, "mobiliario": 1500.0, "equipo": 6000.0}</t>
+          <t>{"equipo": 0.8, "mobiliario": 0.2}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fianza</t>
+          <t>activo_inicial</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>{"marca": 500.0, "aplicaciones": 5000.0, "mobiliario": 1500.0, "equipo": 6000.0}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>capital_fundadores</t>
+          <t>fianza</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>1000.0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prima_fundadores</t>
+          <t>capital_fundadores</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>57000.0</t>
+          <t>3000.0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gastos_constitucion</t>
+          <t>prima_fundadores</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>37000.0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>enisa</t>
+          <t>gastos_constitucion</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{"importe": 38000.0, "interes": 0.06, "carencia_meses": 24, "plazo_meses": 84, "comision_apertura": 0.005, "mes_cobro": 6}</t>
+          <t>1500.0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>banco</t>
+          <t>enisa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{"importe": 20000.0, "interes": 0.065, "carencia_meses": 12, "plazo_meses": 60}</t>
+          <t>{"importe": 35000.0, "interes": 0.06, "carencia_meses": 24, "plazo_meses": 84, "comision_apertura": 0.005, "mes_cobro": 6}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ronda</t>
+          <t>banco</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{"mes": 12, "importe": 250000.0, "participacion": 0.25, "gastos": 3000.0}</t>
+          <t>{"importe": 20000.0, "interes": 0.065, "carencia_meses": 12, "plazo_meses": 60}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iva</t>
+          <t>ronda</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>{"mes": 12, "importe": 250000.0, "participacion": 0.25, "gastos": 3000.0}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tipo_is</t>
+          <t>iva</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.21</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>tipo_is</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>mes_pago_is</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>7</t>
         </is>

--- a/experimentos/plan_financiero/salida/detalle_v11.xlsx
+++ b/experimentos/plan_financiero/salida/detalle_v11.xlsx
@@ -6428,7 +6428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6827,6 +6827,30 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ipc_licencia</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>contrataciones_ligadas</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>{"13": 3, "25": 9}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/experimentos/plan_financiero/salida/detalle_v11.xlsx
+++ b/experimentos/plan_financiero/salida/detalle_v11.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance momento 0" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance año 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance año 2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance año 3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resultados agregada" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resultados año 1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resultados año 2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resultados año 3" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tesorería año 1" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tesorería año 2" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tesorería año 3" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balances" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supuestos" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Balance momento 0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Balance año 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Balance año 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Balance año 3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Resultados agregada" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Resultados año 1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Resultados año 2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Resultados año 3" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Tesorería año 1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Tesorería año 2" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Tesorería año 3" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Mensual" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Balances" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Supuestos" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>7389.333125</v>
+        <v>7389.333124999999</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>7597.377500000001</v>
+        <v>7597.3775</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7597.377500000001</v>
+        <v>7597.3775</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>7805.421875</v>
@@ -1410,22 +1410,22 @@
         <v>7805.421875</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>8013.46625</v>
+        <v>8013.466249999999</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>8013.46625</v>
+        <v>8013.466249999999</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>8221.510625000001</v>
+        <v>8221.510624999999</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8013.46625</v>
+        <v>8013.466249999999</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>8221.510625000001</v>
+        <v>8221.510624999999</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>8221.510625000001</v>
+        <v>8221.510624999999</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>8429.555</v>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3264.699375000001</v>
+        <v>3264.699375000002</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
@@ -2012,7 +2012,7 @@
         <v>342982.244375</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>319324.6768749999</v>
+        <v>319324.676875</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>335277.2356944444</v>
@@ -3200,19 +3200,19 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>319232.0866666666</v>
+        <v>319232.0866666667</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>305620.4719444444</v>
+        <v>305620.4719444445</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>327154.5697916666</v>
+        <v>327154.5697916667</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>319465.3964583333</v>
+        <v>319465.3964583334</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>329220.9638194444</v>
+        <v>329220.9638194445</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>374122.24375</v>
@@ -7921,7 +7921,7 @@
         <v>3650</v>
       </c>
       <c r="X20" t="n">
-        <v>363954.82</v>
+        <v>363954.81</v>
       </c>
     </row>
     <row r="21">
@@ -8187,10 +8187,10 @@
         <v>-14248.62</v>
       </c>
       <c r="N24" t="n">
-        <v>225235.13</v>
+        <v>225235.12</v>
       </c>
       <c r="O24" t="n">
-        <v>260235.13</v>
+        <v>260235.12</v>
       </c>
       <c r="P24" t="n">
         <v>2000</v>
@@ -8557,10 +8557,10 @@
         <v>1759.58</v>
       </c>
       <c r="N29" t="n">
-        <v>230618.88</v>
+        <v>230618.87</v>
       </c>
       <c r="O29" t="n">
-        <v>265618.88</v>
+        <v>265618.87</v>
       </c>
       <c r="P29" t="n">
         <v>2000</v>
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>-46016.25</v>
+        <v>-46016.25000000003</v>
       </c>
     </row>
     <row r="18">
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>-56640.70833333334</v>
+        <v>-56640.7083333334</v>
       </c>
     </row>
     <row r="18">
@@ -11035,10 +11035,10 @@
         <v>31200</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>56800</v>
+        <v>56800.00000000001</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>75600</v>
+        <v>75600.00000000001</v>
       </c>
     </row>
     <row r="15">
@@ -11188,7 +11188,7 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Impuesto de sociedades (25 %, con las bases negativas compensadas)</t>
+          <t>Impuesto de sociedades (15 %, con las bases negativas compensadas)</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -12194,7 +12194,7 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Impuesto de sociedades (25 %, con las bases negativas compensadas)</t>
+          <t>Impuesto de sociedades (15 %, con las bases negativas compensadas)</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -13358,7 +13358,7 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Impuesto de sociedades (25 %, con las bases negativas compensadas)</t>
+          <t>Impuesto de sociedades (15 %, con las bases negativas compensadas)</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -14060,40 +14060,40 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>6300</v>
+        <v>6300.000000000001</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6300</v>
+        <v>6300.000000000001</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6300</v>
+        <v>6300.000000000001</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6300</v>
+        <v>6300.000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>6300</v>
+        <v>6300.000000000001</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>6300</v>
+        <v>6300.000000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>6300</v>
+        <v>6300.000000000001</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6300</v>
+        <v>6300.000000000001</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>6300</v>
+        <v>6300.000000000001</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>6300</v>
+        <v>6300.000000000001</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6300</v>
+        <v>6300.000000000001</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>6300</v>
+        <v>6300.000000000001</v>
       </c>
       <c r="O14" s="3">
         <f>SUM(C14:N14)</f>
@@ -14522,7 +14522,7 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Impuesto de sociedades (25 %, con las bases negativas compensadas)</t>
+          <t>Impuesto de sociedades (15 %, con las bases negativas compensadas)</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
